--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611F0513-F73D-4258-8782-2A5A8860E424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB2F2EF-49F4-4B32-BCB4-FC9BFF50304A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 19-12-2025'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 29-01-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB2F2EF-49F4-4B32-BCB4-FC9BFF50304A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC0DDEB-B730-4550-9313-B76611A5AE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 29-01-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 02-02-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EC0DDEB-B730-4550-9313-B76611A5AE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D04FB57-6850-4D4D-8804-0D3766543CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 02-02-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 20-02-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D04FB57-6850-4D4D-8804-0D3766543CEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B19FD8-0CA3-4D20-95D7-4F8C044DC2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-02-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 20-02-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 04-03-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8B19FD8-0CA3-4D20-95D7-4F8C044DC2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA0BC47-5890-48D8-9CFE-F0C27BC1FD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 04-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 04-03-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 06-03-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA0BC47-5890-48D8-9CFE-F0C27BC1FD4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88B52DE-86BC-4C94-978E-8DE46F713A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88B52DE-86BC-4C94-978E-8DE46F713A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAE77C7-C53D-479A-8C80-4EABB0101D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABAE77C7-C53D-479A-8C80-4EABB0101D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E47AB3-7B6D-491B-A148-B37DC9570FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 06-03-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 09-03-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E47AB3-7B6D-491B-A148-B37DC9570FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383F2BEF-7B3C-439E-B991-A4993961ADDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{383F2BEF-7B3C-439E-B991-A4993961ADDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359C7FE0-1DE2-4809-BABE-CD8C9E354062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 09-03-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 11-03-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359C7FE0-1DE2-4809-BABE-CD8C9E354062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C51541-4300-454E-A639-B97BFAAF159D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C51541-4300-454E-A639-B97BFAAF159D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B583FA22-F536-4B0C-A07E-8CE3FBCF7856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 11-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 11-03-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 20-03-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B583FA22-F536-4B0C-A07E-8CE3FBCF7856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C912B66-F9F8-405B-8918-A2DDF42B31B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 20-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 20-03-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 25-03-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C912B66-F9F8-405B-8918-A2DDF42B31B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927781D3-B356-448D-A062-4756E955157C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-03-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 25-03-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 08-04-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927781D3-B356-448D-A062-4756E955157C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7014FA47-351B-415B-94D9-1E23CB3D48FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 08-04-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 10-04-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7014FA47-351B-415B-94D9-1E23CB3D48FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A2FDD4-7A6D-40AC-B6B3-2DC8F331C7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A2FDD4-7A6D-40AC-B6B3-2DC8F331C7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A79FED-B97F-4FDF-9264-30E6CE855671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 10-04-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 14-04-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A79FED-B97F-4FDF-9264-30E6CE855671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637CF9D5-E83A-4F11-A55C-05DBFA1AC94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 14-04-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 24-04-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{637CF9D5-E83A-4F11-A55C-05DBFA1AC94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87619808-8DD0-48CB-9E7A-A9555D0ED7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87619808-8DD0-48CB-9E7A-A9555D0ED7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD70E9C-1495-46BD-B465-8DFC08C95F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 24-04-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 27-04-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD70E9C-1495-46BD-B465-8DFC08C95F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A137CD-A099-4E35-AF83-AA5B16129C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-04-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 27-04-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 06-05-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A137CD-A099-4E35-AF83-AA5B16129C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAF000A-0294-42A5-B4D4-D3EEDBD848A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-05-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 06-05-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 01-06-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEAF000A-0294-42A5-B4D4-D3EEDBD848A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8B2067-E95C-4C50-B3B3-E4A7F475DDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 01-06-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 02-06-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB8B2067-E95C-4C50-B3B3-E4A7F475DDEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E3028C-BEFE-4323-AB0A-BD0C5B0D1EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E3028C-BEFE-4323-AB0A-BD0C5B0D1EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD4A5F14-1FA9-452E-B138-953AC21E42D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 05-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 02-06-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 05-06-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB2F2EF-49F4-4B32-BCB4-FC9BFF50304A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08460DA6-B912-45F8-B567-BA692F0061BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F209D3-6119-424B-9CB0-775EDEBA8312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9285F7A-6386-4055-89E5-82ECDECF8E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9285F7A-6386-4055-89E5-82ECDECF8E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB0A47D-345B-4926-B4C8-E273D9F170CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB0A47D-345B-4926-B4C8-E273D9F170CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0905C0CB-EB5A-494D-B6E9-A48A2448C563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 09-06-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 15-06-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0905C0CB-EB5A-494D-B6E9-A48A2448C563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E64795-7CD1-450F-8B70-4AEB3A9887BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 15-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 15-06-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 22-06-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E64795-7CD1-450F-8B70-4AEB3A9887BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3C09B0-2C2F-44A4-A540-AA88B08B4284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 22-06-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 23-06-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC3C09B0-2C2F-44A4-A540-AA88B08B4284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8888A15-4DAC-4B6B-9DCC-E25E7B590008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E64795-7CD1-450F-8B70-4AEB3A9887BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF9252B-ADE4-4AD8-8CB5-5108A0B9E76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 22-06-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 23-06-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF9252B-ADE4-4AD8-8CB5-5108A0B9E76B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC78DD1-5709-4A08-A2EA-30897F8C7B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 23-06-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 25-06-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC78DD1-5709-4A08-A2EA-30897F8C7B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43007540-178D-49B7-8FFF-2ECB58620E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 25-06-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 30-06-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43007540-178D-49B7-8FFF-2ECB58620E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AC14FF-0AA1-4C93-A411-D03F5193325E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AC14FF-0AA1-4C93-A411-D03F5193325E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B00D75-60D7-4DFE-B6AE-B8999A81D911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 30-06-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 01-07-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B00D75-60D7-4DFE-B6AE-B8999A81D911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F5BDD3-2686-4EEB-988B-1E510C279CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 01-07-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 02-07-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B00D75-60D7-4DFE-B6AE-B8999A81D911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E308D5-C76A-422A-894E-4F9D3B2E0DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 01-07-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 03-07-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F5BDD3-2686-4EEB-988B-1E510C279CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9870540D-8EBE-47E8-98CE-7E0E828C67A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 02-07-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 03-07-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9870540D-8EBE-47E8-98CE-7E0E828C67A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5DAC8C-5806-4BF0-AB63-4063BBC149C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 03-07-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 09-07-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D5DAC8C-5806-4BF0-AB63-4063BBC149C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D176BEAE-80A2-4029-B2AB-B129AC8F5310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 09-07-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 19-08-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D176BEAE-80A2-4029-B2AB-B129AC8F5310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C90DE7F-4E15-41FD-B18E-4AE7BD40F0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 19-08-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 21-08-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C90DE7F-4E15-41FD-B18E-4AE7BD40F0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72DC7B1-AD9E-40D0-94CC-39EDE1BF0661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="945" windowWidth="21600" windowHeight="12450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 21-08-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 27-08-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -398,9 +398,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -440,7 +440,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D72DC7B1-AD9E-40D0-94CC-39EDE1BF0661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720AAB24-4556-4F7C-A15F-7528DCF98A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 27-08-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 27-08-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 02-09-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720AAB24-4556-4F7C-A15F-7528DCF98A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CDF833-595E-43DD-B4DD-6AAF4E9082B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 02-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 06-09-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75CDF833-595E-43DD-B4DD-6AAF4E9082B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091EDBF1-4B64-4AB7-ACAA-400FB5D17EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091EDBF1-4B64-4AB7-ACAA-400FB5D17EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8B5491-4D84-4392-B4DE-8299437874C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 06-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 07-09-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8B5491-4D84-4392-B4DE-8299437874C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C331B07D-02F7-4039-AFCB-600AF96AC09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="VANS_leverandører">'Opdateret d. 07-09-2026'!$A$1:$F$3</definedName>
+    <definedName name="VANS_leverandører">'Opdateret d. 09-09-2026'!$A$1:$F$3</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/VANS-leverandører_excel.XLSX
+++ b/html/VANS-leverandører_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C331B07D-02F7-4039-AFCB-600AF96AC09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3099FFBA-2899-40DC-97A8-8ADBF3E759FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
